--- a/output/laminas_comunales/comunal_o_ocup_a_2024_aysen.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2024_aysen.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C99"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,7 +384,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>39.2959770114943</v>
+        <v>55.9668988929931</v>
       </c>
     </row>
     <row r="3">
@@ -399,127 +399,1447 @@
         </is>
       </c>
       <c r="C3">
-        <v>37.5733196924603</v>
+        <v>55.6821729628473</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>11201</t>
+          <t>11101</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Coyhaique</t>
         </is>
       </c>
       <c r="C4">
-        <v>36.7900067328491</v>
+        <v>55.4899481993093</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>11202</t>
+          <t>11201</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cisnes</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="C5">
-        <v>33.1509216589862</v>
+        <v>54.8943695631393</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>11301</t>
+          <t>11201</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cochrane</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="C6">
-        <v>30.3677172874881</v>
+        <v>53.9069506726457</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>11102</t>
+          <t>11201</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lago Verde</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="C7">
-        <v>29.9064403829417</v>
+        <v>53.6616557051884</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>11303</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tortel</t>
+          <t>Cisnes</t>
         </is>
       </c>
       <c r="C8">
-        <v>28.9838337182448</v>
+        <v>51.833753678016</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>11401</t>
+          <t>11101</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Chile Chico</t>
+          <t>Coyhaique</t>
         </is>
       </c>
       <c r="C9">
-        <v>27.2822195704057</v>
+        <v>49.8490918803419</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>11203</t>
+          <t>11101</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Guaitecas</t>
+          <t>Coyhaique</t>
         </is>
       </c>
       <c r="C10">
-        <v>27.1490164376179</v>
+        <v>49.7223538080952</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>11302</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>49.0625</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>11302</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>49.0358948357368</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>11301</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Cochrane</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>46.8721461187215</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>11201</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>46.8181818181818</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>11201</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>46.2272713745797</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>11401</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Chile Chico</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>45.1990049751244</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>11201</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>44.2551143200963</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>11203</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Guaitecas</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>43.912037037037</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>11302</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>42.6277146736074</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>11402</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Río Ibáñez</t>
         </is>
       </c>
-      <c r="C11">
+      <c r="C20">
+        <v>41.522324865281</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>11102</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Lago Verde</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>41.2186379928315</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>11303</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Tortel</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>40.7142857142857</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>11102</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Lago Verde</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>40.1741293532338</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>11302</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>39.9717514124294</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>11201</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>39.6424903544564</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>11302</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>39.5114942528736</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>11302</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>39.2959770114943</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>11302</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>39.0804597701149</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>11201</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>38.517809641212</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>11101</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Coyhaique</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>38.2471166141264</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>11101</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Coyhaique</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>38.1698014433684</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>11202</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Cisnes</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>37.950908597776</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>11101</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Coyhaique</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>37.5733196924603</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>11101</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Coyhaique</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>37.4656127352089</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>11401</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Chile Chico</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>36.9913225613405</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>11201</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>36.9787289287935</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>11101</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Coyhaique</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>36.9265915691493</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>11302</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>36.8623352453438</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>11201</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>36.7900067328491</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>11101</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Coyhaique</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>36.7877838966274</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>11202</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Cisnes</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>36.2074209245742</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>11201</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>35.7508245271589</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>11201</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>35.7418629823437</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>11301</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Cochrane</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>35.4670912951168</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>11201</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>34.4825906988069</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>11201</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>33.7477797513321</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>11303</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Tortel</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>33.7378640776699</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>11102</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Lago Verde</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>33.2528180354267</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>11202</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Cisnes</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>33.1509216589862</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>11201</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>32.7686875043703</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>11402</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Río Ibáñez</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>32.6</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>11301</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Cochrane</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>32.5519257914902</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>11302</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>31.1489616054101</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>11302</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>31.0805976284634</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>11301</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Cochrane</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>30.3677172874881</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>11102</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Lago Verde</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>29.9064403829417</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>11202</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Cisnes</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>29.7575634792004</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>11303</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Tortel</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>29.1666666666667</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>11303</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Tortel</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>28.9838337182448</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>11401</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Chile Chico</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>28.9139005468651</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>11303</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Tortel</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>28.8148148148148</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>11301</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Cochrane</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>28.4022863364181</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>11201</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>28.1052237947302</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>11203</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Guaitecas</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>27.710843373494</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>11302</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>27.5462962962963</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>11201</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>27.5373676797965</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>11401</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Chile Chico</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>27.2822195704057</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>11402</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Río Ibáñez</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>27.2128060263653</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>11203</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Guaitecas</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>27.1490164376179</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>11101</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Coyhaique</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>27.0900744977049</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>11101</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Coyhaique</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>27.0571386057585</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>11201</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>26.7241501366294</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>11203</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Guaitecas</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>26.4979639325189</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>11102</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Lago Verde</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>25.9706439393939</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>11402</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Río Ibáñez</t>
+        </is>
+      </c>
+      <c r="C75">
         <v>25.8415110266962</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>11202</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Cisnes</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>25.8203445447088</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>11401</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Chile Chico</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>25.505470156488</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>11302</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>24.5833333333333</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>11203</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Guaitecas</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>24.4281045751634</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>11301</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Cochrane</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>24.2130750605327</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>11102</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Lago Verde</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>24.1776315789474</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>11402</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Río Ibáñez</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>24.0940724742021</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>11203</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Guaitecas</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>23.8425925925926</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>11401</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Chile Chico</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>22.4483502929386</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>11303</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Tortel</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>21.9109195402299</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>11402</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Río Ibáñez</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>21.5562565720294</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>11102</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Lago Verde</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>15.3817914831131</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>11101</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Coyhaique</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>12.3905779692376</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>11101</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Coyhaique</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>12.3332489023978</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>11302</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>11.4523841098636</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>11201</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>11.448060486522</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>11201</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>11.4329710975591</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>11303</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Tortel</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>11.2612612612613</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>11201</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>11.2564300411523</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>11202</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Cisnes</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>10.5884879725086</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>11203</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Guaitecas</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>10.4674796747967</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>11301</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Cochrane</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>8.77305877305877</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>11402</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Río Ibáñez</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>8.35174953959484</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>11401</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Chile Chico</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>7.51237067026541</v>
       </c>
     </row>
   </sheetData>
